--- a/artifacts/results/comparison_report_20260228_185711.xlsx
+++ b/artifacts/results/comparison_report_20260228_185711.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="responses" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="retrieval" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="references" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="responses_raw" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="retrieval" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="references" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,92 +428,113 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>run_name</t>
+          <t>Question</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>provider</t>
+          <t>qwen_rag</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>model_name</t>
+          <t>qwen_no_rag</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>rag_enabled</t>
+          <t>tinyllama_rag</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>tinyllama_no_rag</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>reference_answer</t>
+          <t>gemini_rag</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>gemini_no_rag</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>latency_seconds</t>
+          <t>qwen_rag_latency_seconds</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>prompt_tokens_estimate</t>
+          <t>qwen_no_rag_latency_seconds</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>tinyllama_rag_latency_seconds</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>error_message</t>
+          <t>tinyllama_no_rag_latency_seconds</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>gemini_rag_latency_seconds</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>gemini_no_rag_latency_seconds</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>qwen_rag_prompt_tokens_estimate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>qwen_no_rag_prompt_tokens_estimate</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>tinyllama_rag_prompt_tokens_estimate</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>tinyllama_no_rag_prompt_tokens_estimate</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>gemini_rag_prompt_tokens_estimate</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>gemini_no_rag_prompt_tokens_estimate</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>qwen_rag</t>
+          <t>Show all companies categorized as Tier 1 and Tier 1/2, and group them by EV Supply Chain Role.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
-        <is>
-          <t>ollama</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>qwen2.5:14b</t>
-        </is>
-      </c>
-      <c r="D2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Show all companies categorized as Tier 1 and Tier 1/2, and group them by EV Supply Chain Role.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
         <is>
           <t>Based on the provided evidence:
 **Tier 1:**
@@ -525,168 +547,13 @@
 Toyota Industries Group (TACG-TICA) is categorized as an OEM parent group footprint but does not fit into the Tier 1 or Tier 1/2 categories based on the given information.</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="I2" t="n">
-        <v>545</v>
-      </c>
-      <c r="J2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>qwen_rag</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ollama</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>qwen2.5:14b</t>
-        </is>
-      </c>
-      <c r="D3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>List the companies involved in Battery Pack activities and include their Category, Location, Product / Service, and Employment.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Based on the provided evidence, there is no explicit mention of companies directly involved in Battery Pack activities. The information given does not specify which companies are specifically engaged in battery pack manufacturing or assembly. Therefore, I cannot list such companies with their respective details as requested. The available data includes companies like First American Resources and SK Battery America but does not detail their involvement in Battery Pack activities explicitly.</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="I3" t="n">
-        <v>530</v>
-      </c>
-      <c r="J3" t="b">
-        <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>qwen_no_rag</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ollama</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>qwen2.5:14b</t>
-        </is>
-      </c>
-      <c r="D4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Show all companies categorized as Tier 1 and Tier 1/2, and group them by EV Supply Chain Role.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>To provide an accurate answer to your request, I would need specific data from the Excel workbook(s) that categorizes companies under "Tier 1" and "Tier 1/2," along with their corresponding "EV Supply Chain Role." Since no evidence or dataset has been provided in this interaction, I cannot extract or display such information.
 If you have a specific Excel file or can provide details from the relevant sheets and columns, please share that so I can assist further.</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="I4" t="n">
-        <v>44</v>
-      </c>
-      <c r="J4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>qwen_no_rag</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ollama</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>qwen2.5:14b</t>
-        </is>
-      </c>
-      <c r="D5" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>List the companies involved in Battery Pack activities and include their Category, Location, Product / Service, and Employment.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>To provide an accurate response to your query about listing companies involved in Battery Pack activities along with their Category, Location, Product/Service, and Employment details, I would need specific data or evidence related to these companies. Since no particular dataset or evidence has been provided here, I cannot list the exact information you're asking for.
-If you have a specific Excel workbook or dataset that contains this information, please provide it so I can assist further.</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="I5" t="n">
-        <v>53</v>
-      </c>
-      <c r="J5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>tinyllama_rag</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ollama</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>tinyllama</t>
-        </is>
-      </c>
-      <c r="D6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Show all companies categorized as Tier 1 and Tier 1/2, and group them by EV Supply Chain Role.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>[Chunk 1] company=Valeo source=GNEM updated excel (1).xlsx::Data row=189
 Company: Valeo | EV Supply Chain Role: Tier 1 automotive components
@@ -708,99 +575,7 @@
 Company: Morgan Corp. | Product / Service: Engine components, turbochargers, exhaust parts and other automotive parts | EV / Battery Relevant: Indirect | Category: Tier 1/2</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="I6" t="n">
-        <v>545</v>
-      </c>
-      <c r="J6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>tinyllama_rag</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ollama</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>tinyllama</t>
-        </is>
-      </c>
-      <c r="D7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>List the companies involved in Battery Pack activities and include their Category, Location, Product / Service, and Employment.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>[Chunk 1] company=First American Resources source=GNEM updated excel (1).xlsx::Data row=56
-Company: First American Resources | Product / Service: Honeycomb material | EV / Battery Relevant: No | Category: Tier 2/3
-[Chunk 2] company=SK Battery America source=GNEM updated excel (1).xlsx::Data row=164
-Company: SK Battery America | Categoorry: Tier 1 | Industry Group: Transportation Equipment | Classification Method: Supplier
-[Chunk 3] company=Hyundai Industrial Co. source=GNEM updated excel (1).xlsx::Data row=82
-Company: Hyundai Industrial Co. | Product / Service: Automotiive batteries | EV / Battery Relevant: Indirect | Categoorry: Tier 1/2
-[Chunk 4] company=Panduit Corp. source=GNEM updated excel (1).xlsx::Data row=139
-Company: Panduit Corp. | Product / Service: Truck bodies and parts | EV / Battery Relevant: No | Categoorry: Tier 1
-[Chunk 5] company=PIOLAX Corp. source=GNEM updated excel (1).xlsx::Data row=145
-Company: PIOLAX Corp. | Product / Service: All terrain vehicles | EV / Battery Relevant: Indirect | Categoorry: Tier 1
-[Chunk 6] company=FREYR Battery source=GNEM updated excel (1).xlsx::Data row=62
-Company: FREYR Battery | Category: Tier 2/3 | Industry Group: Fabricaed Metal Products | Classification Method: Supplier
-[Chunk 7] company=Suhner Manufacturing Corp. source=GNEM updated excel (1).xlsx::Data row=170
-Company: Suhner Manufacturing Corp. | Product / Service: Truck trailers | EV / Battery Relevant: No | Category: Tier 1
-[Chunk 8] company=TDK Components USA Inc. source=GNEM updated excel (1).xlsx::Data row=176
-Company: TDK Components USA Inc. | Product / Service: Auto manufacturer headquaarters | EV / Battery Relevant: No | Category: OEM</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="I7" t="n">
-        <v>530</v>
-      </c>
-      <c r="J7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>tinyllama_no_rag</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ollama</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>tinyllama</t>
-        </is>
-      </c>
-      <c r="D8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Show all companies categorized as Tier 1 and Tier 1/2, and group them by EV Supply Chain Role.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Sure! Here's the answer to the user question:
 Question: Show all companies categorized as Tier 1 and Tier 1/2, and group them by EV Supply Chain Role (EV Supply Chain Rolename)
@@ -824,43 +599,102 @@
 With these steps, we can get the data for this answer by selecting all rows containing company names in the "Tier 1/2 Companies" and "All Companies" worksheets, copying their values into the "Tier 1/2 Companies" workbook, then pasting them back into the "All Companies" workbook.</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>The workbook evidence provides the following companies categorized as Tier 1 or Tier 1/2:
+**OEM parent group footprint</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>**Battery Manufacturer:**
+*   Company A
+*   Company D
+*   Company J
+**Raw Material Supplier:**
+*   Company C
+*   Company G
+**Charging Infrastructure:**
+*   Company F
+**Vehicle Manufacturer:**
+*   Company H</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="K2" t="n">
         <v>1.39</v>
       </c>
-      <c r="I8" t="n">
+      <c r="L2" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="N2" t="n">
+        <v>545</v>
+      </c>
+      <c r="O2" t="n">
         <v>44</v>
       </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>tinyllama_no_rag</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ollama</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>tinyllama</t>
-        </is>
-      </c>
-      <c r="D9" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="P2" t="n">
+        <v>545</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>44</v>
+      </c>
+      <c r="R2" t="n">
+        <v>545</v>
+      </c>
+      <c r="S2" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>List the companies involved in Battery Pack activities and include their Category, Location, Product / Service, and Employment.</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Based on the provided evidence, there is no explicit mention of companies directly involved in Battery Pack activities. The information given does not specify which companies are specifically engaged in battery pack manufacturing or assembly. Therefore, I cannot list such companies with their respective details as requested. The available data includes companies like First American Resources and SK Battery America but does not detail their involvement in Battery Pack activities explicitly.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>To provide an accurate response to your query about listing companies involved in Battery Pack activities along with their Category, Location, Product/Service, and Employment details, I would need specific data or evidence related to these companies. Since no particular dataset or evidence has been provided here, I cannot list the exact information you're asking for.
+If you have a specific Excel workbook or dataset that contains this information, please provide it so I can assist further.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[Chunk 1] company=First American Resources source=GNEM updated excel (1).xlsx::Data row=56
+Company: First American Resources | Product / Service: Honeycomb material | EV / Battery Relevant: No | Category: Tier 2/3
+[Chunk 2] company=SK Battery America source=GNEM updated excel (1).xlsx::Data row=164
+Company: SK Battery America | Categoorry: Tier 1 | Industry Group: Transportation Equipment | Classification Method: Supplier
+[Chunk 3] company=Hyundai Industrial Co. source=GNEM updated excel (1).xlsx::Data row=82
+Company: Hyundai Industrial Co. | Product / Service: Automotiive batteries | EV / Battery Relevant: Indirect | Categoorry: Tier 1/2
+[Chunk 4] company=Panduit Corp. source=GNEM updated excel (1).xlsx::Data row=139
+Company: Panduit Corp. | Product / Service: Truck bodies and parts | EV / Battery Relevant: No | Categoorry: Tier 1
+[Chunk 5] company=PIOLAX Corp. source=GNEM updated excel (1).xlsx::Data row=145
+Company: PIOLAX Corp. | Product / Service: All terrain vehicles | EV / Battery Relevant: Indirect | Categoorry: Tier 1
+[Chunk 6] company=FREYR Battery source=GNEM updated excel (1).xlsx::Data row=62
+Company: FREYR Battery | Category: Tier 2/3 | Industry Group: Fabricaed Metal Products | Classification Method: Supplier
+[Chunk 7] company=Suhner Manufacturing Corp. source=GNEM updated excel (1).xlsx::Data row=170
+Company: Suhner Manufacturing Corp. | Product / Service: Truck trailers | EV / Battery Relevant: No | Category: Tier 1
+[Chunk 8] company=TDK Components USA Inc. source=GNEM updated excel (1).xlsx::Data row=176
+Company: TDK Components USA Inc. | Product / Service: Auto manufacturer headquaarters | EV / Battery Relevant: No | Category: OEM</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>Question: What companies are involved in Battery Pack activities and what are their categories, locations, products/services, and employment numbers?
 Answer: The provided evidence indicates that the following companies are involved in Battery Pack activities:
@@ -876,6 +710,515 @@
 Note that the provided evidence is not exhaustive, and additional companies may be involved in Battery Pack activities.</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>The provided evidence does not contain information about companies specifically involved in "Battery Pack activities". Additionally, the evidence does not include Location or Employment details for any of the listed companies.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Here are the companies involved in Battery Pack activities:
+*   **LG Energy Solution**
+    *   Category: Battery Manufacturer</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="N3" t="n">
+        <v>530</v>
+      </c>
+      <c r="O3" t="n">
+        <v>53</v>
+      </c>
+      <c r="P3" t="n">
+        <v>530</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>53</v>
+      </c>
+      <c r="R3" t="n">
+        <v>530</v>
+      </c>
+      <c r="S3" t="n">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>run_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>provider</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>model_name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>rag_enabled</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>reference_answer</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>latency_seconds</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>prompt_tokens_estimate</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>error_message</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>qwen_rag</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>qwen2.5:14b</t>
+        </is>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Show all companies categorized as Tier 1 and Tier 1/2, and group them by EV Supply Chain Role.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Based on the provided evidence:
+**Tier 1:**
+- Valeo | EV Supply Chain Role: Tier 1 automotive components
+- Racemark International LLC | Product / Service: Manufacturing and R&amp;D engine parts for EV | EV / Battery Relevant: Yes | Category: Tier 1
+- Southern Switches Corp. | Product / Service: Commercial truck bodies | EV / Battery Relevant: No | Category: Tier 1
+- Morgan Corp. | Product / Service: Engine components, turbochargers, exhaust parts and other automotive parts | EV / Battery Relevant: Indirect | Category: Tier 1
+**Tier 1/2:**
+- Hyundai Motor Group | Category: Tier 1/2 | Industry Group: Electronic and Other Electrical Equipment and Components | Classification Method: Supplier
+Toyota Industries Group (TACG-TICA) is categorized as an OEM parent group footprint but does not fit into the Tier 1 or Tier 1/2 categories based on the given information.</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="I2" t="n">
+        <v>545</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>qwen_rag</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>qwen2.5:14b</t>
+        </is>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>List the companies involved in Battery Pack activities and include their Category, Location, Product / Service, and Employment.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Based on the provided evidence, there is no explicit mention of companies directly involved in Battery Pack activities. The information given does not specify which companies are specifically engaged in battery pack manufacturing or assembly. Therefore, I cannot list such companies with their respective details as requested. The available data includes companies like First American Resources and SK Battery America but does not detail their involvement in Battery Pack activities explicitly.</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I3" t="n">
+        <v>530</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>qwen_no_rag</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>qwen2.5:14b</t>
+        </is>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Show all companies categorized as Tier 1 and Tier 1/2, and group them by EV Supply Chain Role.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>To provide an accurate answer to your request, I would need specific data from the Excel workbook(s) that categorizes companies under "Tier 1" and "Tier 1/2," along with their corresponding "EV Supply Chain Role." Since no evidence or dataset has been provided in this interaction, I cannot extract or display such information.
+If you have a specific Excel file or can provide details from the relevant sheets and columns, please share that so I can assist further.</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I4" t="n">
+        <v>44</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>qwen_no_rag</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>qwen2.5:14b</t>
+        </is>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>List the companies involved in Battery Pack activities and include their Category, Location, Product / Service, and Employment.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>To provide an accurate response to your query about listing companies involved in Battery Pack activities along with their Category, Location, Product/Service, and Employment details, I would need specific data or evidence related to these companies. Since no particular dataset or evidence has been provided here, I cannot list the exact information you're asking for.
+If you have a specific Excel workbook or dataset that contains this information, please provide it so I can assist further.</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I5" t="n">
+        <v>53</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tinyllama_rag</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>tinyllama</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Show all companies categorized as Tier 1 and Tier 1/2, and group them by EV Supply Chain Role.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>[Chunk 1] company=Valeo source=GNEM updated excel (1).xlsx::Data row=189
+Company: Valeo | EV Supply Chain Role: Tier 1 automotive components
+[Chunk 2] company=EVCO Plastics source=GNEM updated excel (1).xlsx::Data row=53
+Company: EVCO Plastics | Categoorry: Tier 2/3 | Industry Group: Primary Metal Industries | Classification Method: Supplier
+[Chunk 3] company=Racemark International LLC source=GNEM updated excel (1).xlsx::Data row=151
+Company: Racemark International LLC | Product / Service: Manufacturing and R&amp;D engine parts for EV | EV / Battery Relevant: Yes | Categoorry: Tier 1
+[Chunk 4] company=Ecoplastic Corporation source=GNEM updated excel (1).xlsx::Data row=48
+Company: Ecoplastic Corporation | Product / Service: Flexible shafts for automotive transmissions | EV / Battery Relevant: Indirect | Categoorry: Tier 2/3
+[Chunk 5] company=Southern Switches Corp. source=GNEM updated excel (1).xlsx::Data row=167
+Company: Southern Switches Corp. | Product / Service: Commercial truck bodies | EV / Battery Relevant: No | Categoorry: Tier 1
+[Chunk 6] company=Hyundai Motor Group source=GNEM updated excel (1).xlsx::Data row=84
+Company: Hyundai Motor Group | Category: Tier 1/2 | Industry Group: Electronic and Other Electrical Equipment and Compoment | Classification Method: Supplier
+[Chunk 7] company=Toyo Taichou Industries Group (TACG-TICA) source=GNEM updated excel (1).xlsx::Data row=186
+Company: Toyota Industries Group (TACG-TICA) | EV Supply Chaing Role: OEM parent group footprint (electric truck strategy)
+[Chunk 8] company=Moran Corp. source=GNEM updated excel (1).xlsx::Data row=120
+Company: Morgan Corp. | Product / Service: Engine components, turbochargers, exhaust parts and other automotive parts | EV / Battery Relevant: Indirect | Category: Tier 1
+[Chunk 9] company=Morgan Corp. source=GNEM updated excel (1).xlsx::Data row=120
+Company: Morgan Corp. | Product / Service: Engine components, turbochargers, exhaust parts and other automotive parts | EV / Battery Relevant: Indirect | Category: Tier 1/2</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I6" t="n">
+        <v>545</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>tinyllama_rag</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>tinyllama</t>
+        </is>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>List the companies involved in Battery Pack activities and include their Category, Location, Product / Service, and Employment.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>[Chunk 1] company=First American Resources source=GNEM updated excel (1).xlsx::Data row=56
+Company: First American Resources | Product / Service: Honeycomb material | EV / Battery Relevant: No | Category: Tier 2/3
+[Chunk 2] company=SK Battery America source=GNEM updated excel (1).xlsx::Data row=164
+Company: SK Battery America | Categoorry: Tier 1 | Industry Group: Transportation Equipment | Classification Method: Supplier
+[Chunk 3] company=Hyundai Industrial Co. source=GNEM updated excel (1).xlsx::Data row=82
+Company: Hyundai Industrial Co. | Product / Service: Automotiive batteries | EV / Battery Relevant: Indirect | Categoorry: Tier 1/2
+[Chunk 4] company=Panduit Corp. source=GNEM updated excel (1).xlsx::Data row=139
+Company: Panduit Corp. | Product / Service: Truck bodies and parts | EV / Battery Relevant: No | Categoorry: Tier 1
+[Chunk 5] company=PIOLAX Corp. source=GNEM updated excel (1).xlsx::Data row=145
+Company: PIOLAX Corp. | Product / Service: All terrain vehicles | EV / Battery Relevant: Indirect | Categoorry: Tier 1
+[Chunk 6] company=FREYR Battery source=GNEM updated excel (1).xlsx::Data row=62
+Company: FREYR Battery | Category: Tier 2/3 | Industry Group: Fabricaed Metal Products | Classification Method: Supplier
+[Chunk 7] company=Suhner Manufacturing Corp. source=GNEM updated excel (1).xlsx::Data row=170
+Company: Suhner Manufacturing Corp. | Product / Service: Truck trailers | EV / Battery Relevant: No | Category: Tier 1
+[Chunk 8] company=TDK Components USA Inc. source=GNEM updated excel (1).xlsx::Data row=176
+Company: TDK Components USA Inc. | Product / Service: Auto manufacturer headquaarters | EV / Battery Relevant: No | Category: OEM</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I7" t="n">
+        <v>530</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tinyllama_no_rag</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>tinyllama</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Show all companies categorized as Tier 1 and Tier 1/2, and group them by EV Supply Chain Role.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sure! Here's the answer to the user question:
+Question: Show all companies categorized as Tier 1 and Tier 1/2, and group them by EV Supply Chain Role (EV Supply Chain Rolename)
+Answer:
+Here are the specific Excel workbooks that contain the data for this answer:
+- "Tier 1 Companies" - This is a workbook containing all companies categorized as Tier 1. It has a worksheet named "Company Name", which contains the company names in column A.
+- "Tier 1/2 Companies" - This is a workbook containing all companies categorized as Tier 1/2. It has a worksheet named "Company Name", which contains the company names in column A.
+To get the data for this answer, we can use the following steps:
+1. Open the "Tier 1 Companies" workbook and select all the rows containing the company names.
+2. Select the "Company Name" worksheet and copy the values from cells B3 to D5.
+3. Paste the copied values into a new Excel workbook named "Tier 1/2 Companies".
+4. Open the "Tier 1/2 Companies" workbook and select all the rows containing the company names.
+5. Select the "Company Name" worksheet and copy the values from cells E3 to F5.
+6. Paste the copied values into a new Excel workbook named "Tier 1 Companies".
+7. Open the "Tier 1 Companies" workbook and select all the rows containing the company names.
+8. Select the "Company Name" worksheet and copy the values from cells G3 to I5.
+9. Paste the copied values into a new Excel workbook named "Tier 2 Companies".
+10. Open the "Tier 2 Companies" workbook and select all the rows containing the company names.
+11. Select the "Company Name" worksheet and copy the values from cells J3 to L5.
+12. Paste the copied values into a new Excel workbook named "All Companies".
+With these steps, we can get the data for this answer by selecting all rows containing company names in the "Tier 1/2 Companies" and "All Companies" worksheets, copying their values into the "Tier 1/2 Companies" workbook, then pasting them back into the "All Companies" workbook.</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I8" t="n">
+        <v>44</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tinyllama_no_rag</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>tinyllama</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>List the companies involved in Battery Pack activities and include their Category, Location, Product / Service, and Employment.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Question: What companies are involved in Battery Pack activities and what are their categories, locations, products/services, and employment numbers?
+Answer: The provided evidence indicates that the following companies are involved in Battery Pack activities:
+- General Electric (GE) - Category: Manufacturing
+- Samsung Electronics Co., Ltd. - Location: South Korea
+- LG Electronics Inc. - Product/Service: Battery Packs
+- Panasonic Corporation - Employment: 1,000+
+- Toshiba Corporation - Employment: 500+
+- Sony Corporation - Employment: 200+
+- Sanyo Electric Co., Ltd. - Employment: 100+
+- Panasonic Corporation - Employment: 100+
+- LG Electronics Inc. - Employment: 100+
+Note that the provided evidence is not exhaustive, and additional companies may be involved in Battery Pack activities.</t>
+        </is>
+      </c>
       <c r="H9" t="n">
         <v>0.5600000000000001</v>
       </c>
@@ -1069,7 +1412,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1754,7 +2097,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
